--- a/Code/Jupiter/Connect4/Logs/PPO/PPO-2000-PPO-L-True-SP_FINALE-PPO_909 - at-2026-04-22 19-22-08-benchmark.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO/PPO-2000-PPO-L-True-SP_FINALE-PPO_909 - at-2026-04-22 19-22-08-benchmark.xlsx
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -2797,6 +2797,65 @@
         <v>1</v>
       </c>
     </row>
+    <row r="41" spans="1:20">
+      <c r="A41">
+        <v>780</v>
+      </c>
+      <c r="B41">
+        <v>0.0002537383413461538</v>
+      </c>
+      <c r="C41">
+        <v>0.0225</v>
+      </c>
+      <c r="D41">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="E41">
+        <v>0.6943166691233689</v>
+      </c>
+      <c r="G41">
+        <v>0.9974358974358974</v>
+      </c>
+      <c r="H41">
+        <v>0.995</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>0.5</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>0.5</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41">
+        <v>0.5</v>
+      </c>
+      <c r="Q41">
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <v>0.5</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
